--- a/keamanan_sistem_informasi/Latihan_STRIDE_DREAD_1.xlsx
+++ b/keamanan_sistem_informasi/Latihan_STRIDE_DREAD_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\FindServices\ksi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\FindServices\keamanan_sistem_informasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5994CA91-B190-4181-9F93-8E28D00F0EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5026111-9767-4EB7-9DB8-F7B847E45B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="172">
+<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="190">
   <ns0:si>
     <ns0:t>Template Latihan STRIDE + DREAD</ns0:t>
   </ns0:si>
@@ -486,6 +486,69 @@
     <ns0:t>Nilai biru pada kolom B boleh diubah dosen. Total DREAD = jumlah lima dimensi (maks 50).</ns0:t>
   </ns0:si>
   <ns0:si>
+    <ns0:t>CVE-2023-28438</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BOLA / IDOR pada Booking Status Update
+BookingController::updateStatus (validasi auth id dikomentari baris 230).</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2024-21516</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SSRF &amp; Unrestricted File Upload
+Upload avatar, review, dan service hanya cek mime type tanpa sanitasi magic byte/SVG.</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2023-45133</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Missing Auth &amp; Replay pada Midtrans Webhook
+PaymentCallbackController CSRF-exempt tanpa nonce/replay prevention.</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2022-31279</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Improper Access Control / BOLA pada Chat
+ChatController::destroy &amp; manipulasi query parameter konteks pesan.</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2023-38035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2022-31129</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2024-21501</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2023-22809</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CVE-2023-34449</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DoS via Heavy Geolocation &amp; Large File Size
+Perhitungan Haversine tanpa cache dan batas upload 10MB per file gambar.</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Stored XSS pada Review, Jasa &amp; Notes
+Input teks ulasan dan catatan booking rentan injeksi script jika ditampilkan tanpa escape.</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Session Hijacking &amp; Insecure Session Config
+SESSION_ENCRYPT=false dan penyimpanan sesi plaintext di tabel MySQL sessions.</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Privilege Escalation via Mass Assignment
+Atribut role diekspos di array $fillable model User (app/Models/User.php:26).</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DoS &amp; Flooding via WebSocket Reverb
+Endpoint testing /api/test-latency tidak dilindungi otorisasi &amp; rate limit.</ns0:t>
+  </ns0:si>
+  <ns0:si>
     <ns0:t>CVE-2023-28438 / CWE-285</ns0:t>
   </ns0:si>
   <ns0:si>
@@ -525,10 +588,10 @@
     <ns0:t>CVE-2023-40028 / CWE-209</ns0:t>
   </ns0:si>
   <ns0:si>
-    <ns0:t>Information Disclosure via APP_DEBUG=true &amp; Logging Error Sensitive Data di Environment Production</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Debug mode aktif menampilkan stack trace, variabel lingkungan, kredensial DB, dan API Key saat terjadi exception.</ns0:t>
+    <ns0:t>[TERMITIGASI] Information Disclosure via APP_DEBUG &amp; Error Trace (Status: Dinonaktifkan di .env)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Termitigasi: Nilai APP_DEBUG telah diubah menjadi false pada .env sehingga detail exception/kredensial tidak lagi terekspos.</ns0:t>
   </ns0:si>
   <ns0:si>
     <ns0:t>CVE-2023-38035 / CWE-770</ns0:t>
@@ -583,7 +646,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,6 +759,12 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -811,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -904,6 +973,10 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -920,15 +993,27 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF9DC3E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -978,19 +1063,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF9DC3E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1207,10 +1279,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1359,9 +1431,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>147600</xdr:colOff>
+      <xdr:colOff>132360</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:rowOff>134550</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1577,16 +1649,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="40"/>
+      <c r="C2" s="34"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41"/>
+      <c r="C3" s="35"/>
     </row>
     <row r="5" spans="2:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
@@ -1704,78 +1776,78 @@
   </ns0:cols>
   <ns0:sheetData>
     <ns0:row r="1" spans="1:19" ht="33.75" customHeight="1" ns3:dyDescent="0.3">
-      <ns0:c r="A1" s="34" t="s">
+      <ns0:c r="A1" s="36" t="s">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="B1" s="34"/>
-      <ns0:c r="C1" s="34"/>
-      <ns0:c r="D1" s="34"/>
-      <ns0:c r="E1" s="34"/>
-      <ns0:c r="F1" s="34"/>
-      <ns0:c r="G1" s="34"/>
-      <ns0:c r="H1" s="34"/>
-      <ns0:c r="I1" s="34"/>
-      <ns0:c r="J1" s="34"/>
-      <ns0:c r="K1" s="34"/>
-      <ns0:c r="L1" s="34"/>
-      <ns0:c r="M1" s="34"/>
-      <ns0:c r="N1" s="34"/>
-      <ns0:c r="O1" s="34"/>
-      <ns0:c r="P1" s="34"/>
-      <ns0:c r="Q1" s="34"/>
-      <ns0:c r="R1" s="34"/>
-      <ns0:c r="S1" s="34"/>
+      <ns0:c r="B1" s="36"/>
+      <ns0:c r="C1" s="36"/>
+      <ns0:c r="D1" s="36"/>
+      <ns0:c r="E1" s="36"/>
+      <ns0:c r="F1" s="36"/>
+      <ns0:c r="G1" s="36"/>
+      <ns0:c r="H1" s="36"/>
+      <ns0:c r="I1" s="36"/>
+      <ns0:c r="J1" s="36"/>
+      <ns0:c r="K1" s="36"/>
+      <ns0:c r="L1" s="36"/>
+      <ns0:c r="M1" s="36"/>
+      <ns0:c r="N1" s="36"/>
+      <ns0:c r="O1" s="36"/>
+      <ns0:c r="P1" s="36"/>
+      <ns0:c r="Q1" s="36"/>
+      <ns0:c r="R1" s="36"/>
+      <ns0:c r="S1" s="36"/>
     </ns0:row>
     <ns0:row r="2" spans="1:19" ns3:dyDescent="0.3">
-      <ns0:c r="A2" s="35" t="s">
+      <ns0:c r="A2" s="37" t="s">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="B2" s="35"/>
-      <ns0:c r="C2" s="35"/>
-      <ns0:c r="D2" s="35"/>
-      <ns0:c r="E2" s="35"/>
-      <ns0:c r="F2" s="35"/>
-      <ns0:c r="G2" s="35"/>
-      <ns0:c r="H2" s="35"/>
-      <ns0:c r="I2" s="35"/>
-      <ns0:c r="J2" s="35"/>
-      <ns0:c r="K2" s="35"/>
-      <ns0:c r="L2" s="35"/>
-      <ns0:c r="M2" s="35"/>
-      <ns0:c r="N2" s="35"/>
-      <ns0:c r="O2" s="35"/>
-      <ns0:c r="P2" s="35"/>
-      <ns0:c r="Q2" s="35"/>
-      <ns0:c r="R2" s="35"/>
-      <ns0:c r="S2" s="35"/>
+      <ns0:c r="B2" s="37"/>
+      <ns0:c r="C2" s="37"/>
+      <ns0:c r="D2" s="37"/>
+      <ns0:c r="E2" s="37"/>
+      <ns0:c r="F2" s="37"/>
+      <ns0:c r="G2" s="37"/>
+      <ns0:c r="H2" s="37"/>
+      <ns0:c r="I2" s="37"/>
+      <ns0:c r="J2" s="37"/>
+      <ns0:c r="K2" s="37"/>
+      <ns0:c r="L2" s="37"/>
+      <ns0:c r="M2" s="37"/>
+      <ns0:c r="N2" s="37"/>
+      <ns0:c r="O2" s="37"/>
+      <ns0:c r="P2" s="37"/>
+      <ns0:c r="Q2" s="37"/>
+      <ns0:c r="R2" s="37"/>
+      <ns0:c r="S2" s="37"/>
     </ns0:row>
     <ns0:row r="3" spans="1:19" ht="15" customHeight="1" ns3:dyDescent="0.3">
-      <ns0:c r="A3" s="36" t="s">
+      <ns0:c r="A3" s="38" t="s">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="B3" s="36"/>
-      <ns0:c r="C3" s="36"/>
-      <ns0:c r="D3" s="37" t="s">
+      <ns0:c r="B3" s="38"/>
+      <ns0:c r="C3" s="38"/>
+      <ns0:c r="D3" s="39" t="s">
         <ns0:v>25</ns0:v>
       </ns0:c>
-      <ns0:c r="E3" s="37"/>
-      <ns0:c r="F3" s="37"/>
-      <ns0:c r="G3" s="37"/>
-      <ns0:c r="H3" s="37"/>
-      <ns0:c r="I3" s="37"/>
-      <ns0:c r="J3" s="37"/>
-      <ns0:c r="K3" s="38" t="s">
+      <ns0:c r="E3" s="39"/>
+      <ns0:c r="F3" s="39"/>
+      <ns0:c r="G3" s="39"/>
+      <ns0:c r="H3" s="39"/>
+      <ns0:c r="I3" s="39"/>
+      <ns0:c r="J3" s="39"/>
+      <ns0:c r="K3" s="40" t="s">
         <ns0:v>26</ns0:v>
       </ns0:c>
-      <ns0:c r="L3" s="38"/>
-      <ns0:c r="M3" s="38"/>
-      <ns0:c r="N3" s="38"/>
-      <ns0:c r="O3" s="38"/>
-      <ns0:c r="P3" s="39" t="s">
+      <ns0:c r="L3" s="40"/>
+      <ns0:c r="M3" s="40"/>
+      <ns0:c r="N3" s="40"/>
+      <ns0:c r="O3" s="40"/>
+      <ns0:c r="P3" s="41" t="s">
         <ns0:v>27</ns0:v>
       </ns0:c>
-      <ns0:c r="Q3" s="39"/>
-      <ns0:c r="R3" s="39"/>
+      <ns0:c r="Q3" s="41"/>
+      <ns0:c r="R3" s="41"/>
       <ns0:c r="S3" s="4" t="s">
         <ns0:v>18</ns0:v>
       </ns0:c>
@@ -1843,11 +1915,11 @@
       <ns0:c r="A5" s="12">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="B5" s="13" t="s">
-        <ns0:v>142</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" s="13" t="s">
-        <ns0:v>143</ns0:v>
+      <ns0:c r="B5" s="42" t="s">
+        <ns0:v>160</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="42" t="s">
+        <ns0:v>161</ns0:v>
       </ns0:c>
       <ns0:c r="D5" s="14">
         <ns0:v>0</ns0:v>
@@ -1896,21 +1968,21 @@
       </ns0:c>
       <ns0:c r="R5" s="12" t="str">
         <ns0:f>IF(P5="","",RANK(P5,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>2</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="S5" s="13" t="s">
-        <ns0:v>144</ns0:v>
+        <ns0:v>162</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A6" s="12">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="B6" s="13" t="s">
-        <ns0:v>145</ns0:v>
-      </ns0:c>
-      <ns0:c r="C6" s="13" t="s">
-        <ns0:v>146</ns0:v>
+      <ns0:c r="B6" s="42" t="s">
+        <ns0:v>163</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="42" t="s">
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="D6" s="14">
         <ns0:v>0</ns0:v>
@@ -1959,21 +2031,21 @@
       </ns0:c>
       <ns0:c r="R6" s="12" t="str">
         <ns0:f>IF(P6="","",RANK(P6,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>8</ns0:v>
+        <ns0:v>7</ns0:v>
       </ns0:c>
       <ns0:c r="S6" s="13" t="s">
-        <ns0:v>147</ns0:v>
+        <ns0:v>165</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="7" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A7" s="12">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="B7" s="13" t="s">
-        <ns0:v>148</ns0:v>
-      </ns0:c>
-      <ns0:c r="C7" s="13" t="s">
-        <ns0:v>149</ns0:v>
+      <ns0:c r="B7" s="42" t="s">
+        <ns0:v>166</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="42" t="s">
+        <ns0:v>167</ns0:v>
       </ns0:c>
       <ns0:c r="D7" s="14">
         <ns0:v>1</ns0:v>
@@ -2022,21 +2094,21 @@
       </ns0:c>
       <ns0:c r="R7" s="12" t="str">
         <ns0:f>IF(P7="","",RANK(P7,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>4</ns0:v>
+        <ns0:v>3</ns0:v>
       </ns0:c>
       <ns0:c r="S7" s="13" t="s">
-        <ns0:v>150</ns0:v>
+        <ns0:v>168</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="8" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A8" s="12">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="B8" s="13" t="s">
-        <ns0:v>151</ns0:v>
-      </ns0:c>
-      <ns0:c r="C8" s="13" t="s">
-        <ns0:v>152</ns0:v>
+      <ns0:c r="B8" s="42" t="s">
+        <ns0:v>169</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" s="42" t="s">
+        <ns0:v>170</ns0:v>
       </ns0:c>
       <ns0:c r="D8" s="14">
         <ns0:v>0</ns0:v>
@@ -2085,21 +2157,21 @@
       </ns0:c>
       <ns0:c r="R8" s="12" t="str">
         <ns0:f>IF(P8="","",RANK(P8,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>10</ns0:v>
+        <ns0:v>9</ns0:v>
       </ns0:c>
       <ns0:c r="S8" s="13" t="s">
-        <ns0:v>153</ns0:v>
+        <ns0:v>171</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="9" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A9" s="12">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="B9" s="13" t="s">
-        <ns0:v>154</ns0:v>
-      </ns0:c>
-      <ns0:c r="C9" s="13" t="s">
-        <ns0:v>155</ns0:v>
+      <ns0:c r="B9" s="42" t="s">
+        <ns0:v>172</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="42" t="s">
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="D9" s="14">
         <ns0:v>0</ns0:v>
@@ -2124,45 +2196,45 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="K9" s="14">
-        <ns0:v>7</ns0:v>
+        <ns0:v>2</ns0:v>
       </ns0:c>
       <ns0:c r="L9" s="14">
-        <ns0:v>9</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="M9" s="14">
-        <ns0:v>9</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="N9" s="14">
-        <ns0:v>9</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="O9" s="14">
-        <ns0:v>9</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="P9" s="12" t="str">
         <ns0:f>IF(COUNT(K9:O9)=5,SUM(K9:O9),"")</ns0:f>
-        <ns0:v>43</ns0:v>
+        <ns0:v>6</ns0:v>
       </ns0:c>
       <ns0:c r="Q9" s="12" t="str">
         <ns0:f>IF(P9="","",IF(P9&gt;=DREAD_Guidelines!$B$13,"CRITICAL",IF(P9&gt;=DREAD_Guidelines!$B$14,"HIGH",IF(P9&gt;=DREAD_Guidelines!$B$15,"MEDIUM","LOW"))))</ns0:f>
-        <ns0:v>CRITICAL</ns0:v>
+        <ns0:v>LOW</ns0:v>
       </ns0:c>
       <ns0:c r="R9" s="12" t="str">
         <ns0:f>IF(P9="","",RANK(P9,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>1</ns0:v>
+        <ns0:v>10</ns0:v>
       </ns0:c>
       <ns0:c r="S9" s="13" t="s">
-        <ns0:v>156</ns0:v>
+        <ns0:v>174</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="10" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A10" s="12">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="B10" s="13" t="s">
-        <ns0:v>157</ns0:v>
-      </ns0:c>
-      <ns0:c r="C10" s="13" t="s">
-        <ns0:v>158</ns0:v>
+      <ns0:c r="B10" s="42" t="s">
+        <ns0:v>175</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" s="42" t="s">
+        <ns0:v>176</ns0:v>
       </ns0:c>
       <ns0:c r="D10" s="14">
         <ns0:v>0</ns0:v>
@@ -2211,21 +2283,21 @@
       </ns0:c>
       <ns0:c r="R10" s="12" t="str">
         <ns0:f>IF(P10="","",RANK(P10,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>5</ns0:v>
+        <ns0:v>4</ns0:v>
       </ns0:c>
       <ns0:c r="S10" s="13" t="s">
-        <ns0:v>159</ns0:v>
+        <ns0:v>177</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="11" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A11" s="12">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="B11" s="13" t="s">
-        <ns0:v>160</ns0:v>
-      </ns0:c>
-      <ns0:c r="C11" s="13" t="s">
-        <ns0:v>161</ns0:v>
+      <ns0:c r="B11" s="42" t="s">
+        <ns0:v>178</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" s="42" t="s">
+        <ns0:v>179</ns0:v>
       </ns0:c>
       <ns0:c r="D11" s="14">
         <ns0:v>1</ns0:v>
@@ -2274,21 +2346,21 @@
       </ns0:c>
       <ns0:c r="R11" s="12" t="str">
         <ns0:f>IF(P11="","",RANK(P11,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>6</ns0:v>
+        <ns0:v>5</ns0:v>
       </ns0:c>
       <ns0:c r="S11" s="13" t="s">
-        <ns0:v>162</ns0:v>
+        <ns0:v>180</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="12" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A12" s="12">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="B12" s="13" t="s">
-        <ns0:v>163</ns0:v>
-      </ns0:c>
-      <ns0:c r="C12" s="13" t="s">
-        <ns0:v>164</ns0:v>
+      <ns0:c r="B12" s="42" t="s">
+        <ns0:v>181</ns0:v>
+      </ns0:c>
+      <ns0:c r="C12" s="42" t="s">
+        <ns0:v>182</ns0:v>
       </ns0:c>
       <ns0:c r="D12" s="14">
         <ns0:v>1</ns0:v>
@@ -2337,21 +2409,21 @@
       </ns0:c>
       <ns0:c r="R12" s="12" t="str">
         <ns0:f>IF(P12="","",RANK(P12,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>8</ns0:v>
+        <ns0:v>7</ns0:v>
       </ns0:c>
       <ns0:c r="S12" s="13" t="s">
-        <ns0:v>165</ns0:v>
+        <ns0:v>183</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="13" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A13" s="12">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="B13" s="13" t="s">
-        <ns0:v>166</ns0:v>
-      </ns0:c>
-      <ns0:c r="C13" s="13" t="s">
-        <ns0:v>167</ns0:v>
+      <ns0:c r="B13" s="42" t="s">
+        <ns0:v>184</ns0:v>
+      </ns0:c>
+      <ns0:c r="C13" s="42" t="s">
+        <ns0:v>185</ns0:v>
       </ns0:c>
       <ns0:c r="D13" s="14">
         <ns0:v>1</ns0:v>
@@ -2400,21 +2472,21 @@
       </ns0:c>
       <ns0:c r="R13" s="12" t="str">
         <ns0:f>IF(P13="","",RANK(P13,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>6</ns0:v>
+        <ns0:v>5</ns0:v>
       </ns0:c>
       <ns0:c r="S13" s="13" t="s">
-        <ns0:v>168</ns0:v>
+        <ns0:v>186</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="14" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="A14" s="12">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="B14" s="13" t="s">
-        <ns0:v>169</ns0:v>
-      </ns0:c>
-      <ns0:c r="C14" s="13" t="s">
-        <ns0:v>170</ns0:v>
+      <ns0:c r="B14" s="42" t="s">
+        <ns0:v>187</ns0:v>
+      </ns0:c>
+      <ns0:c r="C14" s="42" t="s">
+        <ns0:v>188</ns0:v>
       </ns0:c>
       <ns0:c r="D14" s="14">
         <ns0:v>1</ns0:v>
@@ -2463,10 +2535,10 @@
       </ns0:c>
       <ns0:c r="R14" s="12" t="str">
         <ns0:f>IF(P14="","",RANK(P14,$P$5:$P$44,0))</ns0:f>
-        <ns0:v>2</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="S14" s="13" t="s">
-        <ns0:v>171</ns0:v>
+        <ns0:v>189</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="15" spans="1:19" ht="21.75" customHeight="1" ns3:dyDescent="0.3">
@@ -3410,7 +3482,7 @@
     <ns0:mergeCell ref="P3:R3"/>
   </ns0:mergeCells>
   <ns0:conditionalFormatting sqref="D5:I44">
-    <ns0:cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <ns0:cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <ns0:formula>1</ns0:formula>
     </ns0:cfRule>
   </ns0:conditionalFormatting>
@@ -3425,16 +3497,16 @@
     </ns0:cfRule>
   </ns0:conditionalFormatting>
   <ns0:conditionalFormatting sqref="Q5:Q44">
-    <ns0:cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <ns0:cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <ns0:formula>"CRITICAL"</ns0:formula>
     </ns0:cfRule>
-    <ns0:cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <ns0:cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <ns0:formula>"HIGH"</ns0:formula>
     </ns0:cfRule>
-    <ns0:cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <ns0:cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <ns0:formula>"MEDIUM"</ns0:formula>
     </ns0:cfRule>
-    <ns0:cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <ns0:cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <ns0:formula>"LOW"</ns0:formula>
     </ns0:cfRule>
   </ns0:conditionalFormatting>
@@ -3482,7 +3554,7 @@
       </ns0:c>
       <ns0:c r="C5" s="17">
         <ns0:f>COUNTIF(STRIDE_DREAD_Template!$Q$5:$Q$44,B5)</ns0:f>
-        <ns0:v>3</ns0:v>
+        <ns0:v>2</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6" spans="2:3" ns3:dyDescent="0.3">
@@ -3509,7 +3581,7 @@
       </ns0:c>
       <ns0:c r="C8" s="17">
         <ns0:f>COUNTIF(STRIDE_DREAD_Template!$Q$5:$Q$44,B8)</ns0:f>
-        <ns0:v>0</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="9" spans="2:3" ns3:dyDescent="0.3">
@@ -3597,7 +3669,7 @@
       </ns0:c>
       <ns0:c r="C20" s="23">
         <ns0:f>IFERROR(AVERAGE(STRIDE_DREAD_Template!P5:P44),0)</ns0:f>
-        <ns0:v>37.5</ns0:v>
+        <ns0:v>33.8</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="21" spans="2:3" ns3:dyDescent="0.3">
@@ -3606,16 +3678,16 @@
       </ns0:c>
       <ns0:c r="C21" s="24">
         <ns0:f>IF(COUNT(STRIDE_DREAD_Template!P5:P44)=0,0,MAX(STRIDE_DREAD_Template!P5:P44))</ns0:f>
-        <ns0:v>43</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22" spans="2:3" ns3:dyDescent="0.3">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22" spans="2:3" ht="79.8" customHeight="1" ns3:dyDescent="0.3">
       <ns0:c r="B22" s="22" t="s">
         <ns0:v>65</ns0:v>
       </ns0:c>
       <ns0:c r="C22" s="25" t="s">
         <ns0:f>IFERROR(INDEX(STRIDE_DREAD_Template!C5:C44,MATCH(1,STRIDE_DREAD_Template!R5:R44,0)),"-")</ns0:f>
-        <ns0:v>155</ns0:v>
+        <ns0:v>161</ns0:v>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
